--- a/ky/downloads/data-excel/3.b.1.xlsx
+++ b/ky/downloads/data-excel/3.b.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F40C580-3561-4AE5-A9A4-094606875A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14340" windowHeight="11760"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.в.1-вакцина" sheetId="1" r:id="rId1"/>
@@ -176,7 +177,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -880,7 +881,7 @@
     <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -897,46 +898,25 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -944,9 +924,6 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -957,7 +934,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="56" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -966,61 +943,37 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="40" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="40" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="40" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="40" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1029,98 +982,104 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="40" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="112">
     <cellStyle name="20% — акцент1" xfId="17" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Акцент1 2" xfId="41"/>
-    <cellStyle name="20% — акцент1 2" xfId="74"/>
-    <cellStyle name="20% - Акцент1 2 2" xfId="61"/>
-    <cellStyle name="20% - Акцент1 2 3" xfId="88"/>
-    <cellStyle name="20% — акцент1 3" xfId="100"/>
+    <cellStyle name="20% - Акцент1 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% — акцент1 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Акцент1 2 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Акцент1 2 3" xfId="88" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% — акцент1 3" xfId="100" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="20% — акцент2" xfId="21" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Акцент2 2" xfId="42"/>
-    <cellStyle name="20% — акцент2 2" xfId="76"/>
-    <cellStyle name="20% - Акцент2 2 2" xfId="62"/>
-    <cellStyle name="20% - Акцент2 2 3" xfId="89"/>
-    <cellStyle name="20% — акцент2 3" xfId="102"/>
+    <cellStyle name="20% - Акцент2 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="20% — акцент2 2" xfId="76" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="20% - Акцент2 2 2" xfId="62" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="20% - Акцент2 2 3" xfId="89" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="20% — акцент2 3" xfId="102" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
     <cellStyle name="20% — акцент3" xfId="25" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Акцент3 2" xfId="43"/>
-    <cellStyle name="20% — акцент3 2" xfId="78"/>
-    <cellStyle name="20% - Акцент3 2 2" xfId="63"/>
-    <cellStyle name="20% - Акцент3 2 3" xfId="90"/>
-    <cellStyle name="20% — акцент3 3" xfId="104"/>
+    <cellStyle name="20% - Акцент3 2" xfId="43" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="20% — акцент3 2" xfId="78" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="20% - Акцент3 2 2" xfId="63" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="20% - Акцент3 2 3" xfId="90" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="20% — акцент3 3" xfId="104" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="20% — акцент4" xfId="29" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Акцент4 2" xfId="44"/>
-    <cellStyle name="20% — акцент4 2" xfId="80"/>
-    <cellStyle name="20% - Акцент4 2 2" xfId="64"/>
-    <cellStyle name="20% - Акцент4 2 3" xfId="91"/>
-    <cellStyle name="20% — акцент4 3" xfId="106"/>
+    <cellStyle name="20% - Акцент4 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="20% — акцент4 2" xfId="80" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="20% - Акцент4 2 2" xfId="64" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="20% - Акцент4 2 3" xfId="91" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="20% — акцент4 3" xfId="106" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
     <cellStyle name="20% — акцент5" xfId="33" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Акцент5 2" xfId="45"/>
-    <cellStyle name="20% — акцент5 2" xfId="82"/>
-    <cellStyle name="20% - Акцент5 2 2" xfId="65"/>
-    <cellStyle name="20% - Акцент5 2 3" xfId="92"/>
-    <cellStyle name="20% — акцент5 3" xfId="108"/>
+    <cellStyle name="20% - Акцент5 2" xfId="45" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="20% — акцент5 2" xfId="82" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="20% - Акцент5 2 2" xfId="65" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="20% - Акцент5 2 3" xfId="92" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="20% — акцент5 3" xfId="108" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
     <cellStyle name="20% — акцент6" xfId="37" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="20% - Акцент6 2" xfId="46"/>
-    <cellStyle name="20% — акцент6 2" xfId="84"/>
-    <cellStyle name="20% - Акцент6 2 2" xfId="66"/>
-    <cellStyle name="20% - Акцент6 2 3" xfId="93"/>
-    <cellStyle name="20% — акцент6 3" xfId="110"/>
+    <cellStyle name="20% - Акцент6 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="20% — акцент6 2" xfId="84" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="20% - Акцент6 2 2" xfId="66" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="20% - Акцент6 2 3" xfId="93" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="20% — акцент6 3" xfId="110" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
     <cellStyle name="40% — акцент1" xfId="18" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Акцент1 2" xfId="47"/>
-    <cellStyle name="40% — акцент1 2" xfId="75"/>
-    <cellStyle name="40% - Акцент1 2 2" xfId="67"/>
-    <cellStyle name="40% - Акцент1 2 3" xfId="94"/>
-    <cellStyle name="40% — акцент1 3" xfId="101"/>
+    <cellStyle name="40% - Акцент1 2" xfId="47" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="40% — акцент1 2" xfId="75" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="40% - Акцент1 2 2" xfId="67" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="40% - Акцент1 2 3" xfId="94" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="40% — акцент1 3" xfId="101" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
     <cellStyle name="40% — акцент2" xfId="22" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Акцент2 2" xfId="48"/>
-    <cellStyle name="40% — акцент2 2" xfId="77"/>
-    <cellStyle name="40% - Акцент2 2 2" xfId="68"/>
-    <cellStyle name="40% - Акцент2 2 3" xfId="95"/>
-    <cellStyle name="40% — акцент2 3" xfId="103"/>
+    <cellStyle name="40% - Акцент2 2" xfId="48" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="40% — акцент2 2" xfId="77" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="40% - Акцент2 2 2" xfId="68" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="40% - Акцент2 2 3" xfId="95" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="40% — акцент2 3" xfId="103" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
     <cellStyle name="40% — акцент3" xfId="26" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Акцент3 2" xfId="49"/>
-    <cellStyle name="40% — акцент3 2" xfId="79"/>
-    <cellStyle name="40% - Акцент3 2 2" xfId="69"/>
-    <cellStyle name="40% - Акцент3 2 3" xfId="96"/>
-    <cellStyle name="40% — акцент3 3" xfId="105"/>
+    <cellStyle name="40% - Акцент3 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="40% — акцент3 2" xfId="79" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="40% - Акцент3 2 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="40% - Акцент3 2 3" xfId="96" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="40% — акцент3 3" xfId="105" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
     <cellStyle name="40% — акцент4" xfId="30" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Акцент4 2" xfId="50"/>
-    <cellStyle name="40% — акцент4 2" xfId="81"/>
-    <cellStyle name="40% - Акцент4 2 2" xfId="70"/>
-    <cellStyle name="40% - Акцент4 2 3" xfId="97"/>
-    <cellStyle name="40% — акцент4 3" xfId="107"/>
+    <cellStyle name="40% - Акцент4 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="40% — акцент4 2" xfId="81" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="40% - Акцент4 2 2" xfId="70" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="40% - Акцент4 2 3" xfId="97" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="40% — акцент4 3" xfId="107" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
     <cellStyle name="40% — акцент5" xfId="34" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Акцент5 2" xfId="51"/>
-    <cellStyle name="40% — акцент5 2" xfId="83"/>
-    <cellStyle name="40% - Акцент5 2 2" xfId="71"/>
-    <cellStyle name="40% - Акцент5 2 3" xfId="98"/>
-    <cellStyle name="40% — акцент5 3" xfId="109"/>
+    <cellStyle name="40% - Акцент5 2" xfId="51" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="40% — акцент5 2" xfId="83" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="40% - Акцент5 2 2" xfId="71" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="40% - Акцент5 2 3" xfId="98" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="40% — акцент5 3" xfId="109" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
     <cellStyle name="40% — акцент6" xfId="38" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="40% - Акцент6 2" xfId="52"/>
-    <cellStyle name="40% — акцент6 2" xfId="85"/>
-    <cellStyle name="40% - Акцент6 2 2" xfId="72"/>
-    <cellStyle name="40% - Акцент6 2 3" xfId="99"/>
-    <cellStyle name="40% — акцент6 3" xfId="111"/>
+    <cellStyle name="40% - Акцент6 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="40% — акцент6 2" xfId="85" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="40% - Акцент6 2 2" xfId="72" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="40% - Акцент6 2 3" xfId="99" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="40% — акцент6 3" xfId="111" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
     <cellStyle name="60% — акцент1" xfId="19" builtinId="32" customBuiltin="1"/>
     <cellStyle name="60% — акцент2" xfId="23" builtinId="36" customBuiltin="1"/>
     <cellStyle name="60% — акцент3" xfId="27" builtinId="40" customBuiltin="1"/>
     <cellStyle name="60% — акцент4" xfId="31" builtinId="44" customBuiltin="1"/>
     <cellStyle name="60% — акцент5" xfId="35" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% — акцент6" xfId="39" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Normal_PPI" xfId="53"/>
+    <cellStyle name="Normal_PPI" xfId="53" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
     <cellStyle name="Акцент1" xfId="16" builtinId="29" customBuiltin="1"/>
     <cellStyle name="Акцент2" xfId="20" builtinId="33" customBuiltin="1"/>
     <cellStyle name="Акцент3" xfId="24" builtinId="37" customBuiltin="1"/>
@@ -1136,21 +1095,21 @@
     <cellStyle name="Заголовок 4" xfId="4" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Итог" xfId="15" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Контрольная ячейка" xfId="12" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Название 2" xfId="55"/>
-    <cellStyle name="Название 3" xfId="54"/>
+    <cellStyle name="Название 2" xfId="55" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Название 3" xfId="54" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
     <cellStyle name="Нейтральный" xfId="7" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="56"/>
-    <cellStyle name="Обычный 2 2" xfId="60"/>
-    <cellStyle name="Обычный 3" xfId="57"/>
-    <cellStyle name="Обычный 3 2" xfId="86"/>
-    <cellStyle name="Обычный 4" xfId="40"/>
+    <cellStyle name="Обычный 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="60" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="Обычный 3" xfId="57" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Обычный 4" xfId="40" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
     <cellStyle name="Плохой" xfId="6" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Пояснение" xfId="14" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Примечание 2" xfId="58"/>
-    <cellStyle name="Примечание 2 2" xfId="73"/>
-    <cellStyle name="Примечание 3" xfId="59"/>
-    <cellStyle name="Примечание 3 2" xfId="87"/>
+    <cellStyle name="Примечание 2" xfId="58" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="Примечание 2 2" xfId="73" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="Примечание 3" xfId="59" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="Примечание 3 2" xfId="87" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
     <cellStyle name="Связанная ячейка" xfId="11" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Текст предупреждения" xfId="13" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Хороший" xfId="5" builtinId="26" customBuiltin="1"/>
@@ -1430,181 +1389,173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U38"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="38.5703125" style="12" customWidth="1"/>
-    <col min="4" max="16" width="7.7109375" style="12" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="3" width="38.5703125" style="8" customWidth="1"/>
+    <col min="4" max="16" width="7.7109375" style="8" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:21" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-    </row>
-    <row r="3" spans="1:20" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="33"/>
-      <c r="T3" s="33"/>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+    </row>
+    <row r="3" spans="1:21" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="42"/>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="13">
         <v>2007</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="13">
         <v>2008</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="13">
         <v>2009</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="13">
         <v>2010</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="13">
         <v>2011</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="13">
         <v>2012</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="13">
         <v>2013</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="13">
         <v>2014</v>
       </c>
-      <c r="L4" s="20">
+      <c r="L4" s="13">
         <v>2015</v>
       </c>
-      <c r="M4" s="20">
+      <c r="M4" s="13">
         <v>2016</v>
       </c>
-      <c r="N4" s="20">
+      <c r="N4" s="13">
         <v>2017</v>
       </c>
-      <c r="O4" s="20">
+      <c r="O4" s="13">
         <v>2018</v>
       </c>
-      <c r="P4" s="20">
+      <c r="P4" s="13">
         <v>2019</v>
       </c>
-      <c r="Q4" s="20">
+      <c r="Q4" s="13">
         <v>2020</v>
       </c>
-      <c r="R4" s="20">
+      <c r="R4" s="13">
         <v>2021</v>
       </c>
-      <c r="S4" s="20">
+      <c r="S4" s="13">
         <v>2022</v>
       </c>
-      <c r="T4" s="20">
+      <c r="T4" s="13">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="36" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
+      <c r="U4" s="43">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="36" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="51"/>
-      <c r="T5" s="51"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="35"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="39"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="14">
         <v>94.1</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="14">
         <v>95.3</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="14">
         <v>95.4</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="14">
         <v>96.5</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="14">
         <v>95.1</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="14">
         <v>96.2</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="14">
         <v>96.9</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="14">
         <v>95.8</v>
       </c>
       <c r="L6" s="3">
@@ -1619,30 +1570,33 @@
       <c r="O6" s="3">
         <v>94.5</v>
       </c>
-      <c r="P6" s="21">
+      <c r="P6" s="14">
         <v>94.351083080525839</v>
       </c>
-      <c r="Q6" s="52">
+      <c r="Q6" s="36">
         <v>88.157250792756912</v>
       </c>
-      <c r="R6" s="52">
+      <c r="R6" s="36">
         <v>88.796593100633856</v>
       </c>
-      <c r="S6" s="52">
+      <c r="S6" s="36">
         <v>91.320113549242663</v>
       </c>
-      <c r="T6" s="52">
+      <c r="T6" s="36">
         <v>87.939982676297319</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" s="35" t="s">
+      <c r="U6" s="44">
+        <v>84.600399745090087</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A7" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="26" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="5">
@@ -1681,30 +1635,33 @@
       <c r="O7" s="5">
         <v>96.6</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="9">
         <v>98.322618783713892</v>
       </c>
-      <c r="Q7" s="53">
+      <c r="Q7" s="37">
         <v>91.684705531089051</v>
       </c>
-      <c r="R7" s="53">
+      <c r="R7" s="37">
         <v>86.908583391486388</v>
       </c>
-      <c r="S7" s="53">
+      <c r="S7" s="37">
         <v>95.532963647566234</v>
       </c>
-      <c r="T7" s="53">
+      <c r="T7" s="37">
         <v>94.667839155807826</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
+      <c r="U7" s="41">
+        <v>95.01321003963011</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="26" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="5">
@@ -1743,30 +1700,33 @@
       <c r="O8" s="5">
         <v>96.1</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="9">
         <v>90.174028583465656</v>
       </c>
-      <c r="Q8" s="53">
+      <c r="Q8" s="37">
         <v>87.415503615268193</v>
       </c>
-      <c r="R8" s="53">
+      <c r="R8" s="37">
         <v>89.680106631122953</v>
       </c>
-      <c r="S8" s="53">
+      <c r="S8" s="37">
         <v>91.979142449101602</v>
       </c>
-      <c r="T8" s="53">
+      <c r="T8" s="37">
         <v>89.354637891678763</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="35" t="s">
+      <c r="U8" s="41">
+        <v>87.430050363738104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="26" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="5">
@@ -1805,30 +1765,33 @@
       <c r="O9" s="5">
         <v>95</v>
       </c>
-      <c r="P9" s="11">
+      <c r="P9" s="9">
         <v>94.575713992192306</v>
       </c>
-      <c r="Q9" s="53">
+      <c r="Q9" s="37">
         <v>87.60435379900666</v>
       </c>
-      <c r="R9" s="53">
+      <c r="R9" s="37">
         <v>95.775910364145659</v>
       </c>
-      <c r="S9" s="53">
+      <c r="S9" s="37">
         <v>97.11736444749485</v>
       </c>
-      <c r="T9" s="53">
+      <c r="T9" s="37">
         <v>90.177417459757962</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="35" t="s">
+      <c r="U9" s="41">
+        <v>91.05935386927122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="26" t="s">
         <v>22</v>
       </c>
       <c r="D10" s="5">
@@ -1867,30 +1830,33 @@
       <c r="O10" s="5">
         <v>94.8</v>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="9">
         <v>97.592920353982308</v>
       </c>
-      <c r="Q10" s="53">
+      <c r="Q10" s="37">
         <v>90.958704748044383</v>
       </c>
-      <c r="R10" s="53">
+      <c r="R10" s="37">
         <v>96.517042279754136</v>
       </c>
-      <c r="S10" s="53">
+      <c r="S10" s="37">
         <v>95.22197889707347</v>
       </c>
-      <c r="T10" s="53">
+      <c r="T10" s="37">
         <v>85.668586052463212</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="35" t="s">
+      <c r="U10" s="41">
+        <v>85.801742406404529</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="26" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="5">
@@ -1929,30 +1895,33 @@
       <c r="O11" s="5">
         <v>95.8</v>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="9">
         <v>99.335639714661852</v>
       </c>
-      <c r="Q11" s="53">
+      <c r="Q11" s="37">
         <v>95.543628277871491</v>
       </c>
-      <c r="R11" s="53">
+      <c r="R11" s="37">
         <v>90.311530128242666</v>
       </c>
-      <c r="S11" s="53">
+      <c r="S11" s="37">
         <v>95.83359340865114</v>
       </c>
-      <c r="T11" s="53">
+      <c r="T11" s="37">
         <v>92.521151660563206</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="35" t="s">
+      <c r="U11" s="41">
+        <v>95.203503899156075</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A12" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="26" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="5">
@@ -1991,30 +1960,33 @@
       <c r="O12" s="5">
         <v>95.3</v>
       </c>
-      <c r="P12" s="11">
+      <c r="P12" s="9">
         <v>92.698706099815155</v>
       </c>
-      <c r="Q12" s="53">
+      <c r="Q12" s="37">
         <v>94.17195614541258</v>
       </c>
-      <c r="R12" s="53">
+      <c r="R12" s="37">
         <v>90.746324915190343</v>
       </c>
-      <c r="S12" s="53">
+      <c r="S12" s="37">
         <v>91.694814226107695</v>
       </c>
-      <c r="T12" s="53">
+      <c r="T12" s="37">
         <v>89.321789321789325</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A13" s="35" t="s">
+      <c r="U12" s="41">
+        <v>82.973459289248765</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A13" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="26" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="5">
@@ -2053,30 +2025,33 @@
       <c r="O13" s="5">
         <v>92.5</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="9">
         <v>91.652621722846433</v>
       </c>
-      <c r="Q13" s="53">
+      <c r="Q13" s="37">
         <v>89.922189931564631</v>
       </c>
-      <c r="R13" s="53">
+      <c r="R13" s="37">
         <v>90.894107952204379</v>
       </c>
-      <c r="S13" s="53">
+      <c r="S13" s="37">
         <v>92.720266061341917</v>
       </c>
-      <c r="T13" s="53">
+      <c r="T13" s="37">
         <v>86.485472284764668</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="35" t="s">
+      <c r="U13" s="41">
+        <v>79.82275676531097</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="26" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="5">
@@ -2115,739 +2090,775 @@
       <c r="O14" s="5">
         <v>90.3</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="9">
         <v>92.01890494025325</v>
       </c>
-      <c r="Q14" s="53">
+      <c r="Q14" s="37">
         <v>73.377390695435253</v>
       </c>
-      <c r="R14" s="53">
+      <c r="R14" s="37">
         <v>81.065680730752504</v>
       </c>
-      <c r="S14" s="53">
+      <c r="S14" s="37">
         <v>78.590540307267389</v>
       </c>
-      <c r="T14" s="53">
+      <c r="T14" s="37">
         <v>76.48370416053892</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="37" t="s">
+      <c r="U14" s="41">
+        <v>74.345272482187568</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>95.2</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="5">
         <v>96.7</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>95.4</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>95.7</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>95.2</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <v>98.5</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="5">
         <v>99.2</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>96</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="5">
         <v>97.6</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="5">
         <v>96.7</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="5">
         <v>98</v>
       </c>
-      <c r="O15" s="6">
+      <c r="O15" s="5">
         <v>95.2</v>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="9">
         <v>95.586032038723062</v>
       </c>
-      <c r="Q15" s="54">
+      <c r="Q15" s="37">
         <v>87.34037868780274</v>
       </c>
-      <c r="R15" s="54">
+      <c r="R15" s="37">
         <v>85.088888888888889</v>
       </c>
-      <c r="S15" s="54">
+      <c r="S15" s="37">
         <v>88.700629650829995</v>
       </c>
-      <c r="T15" s="54">
+      <c r="T15" s="37">
         <v>86.049943246311017</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+      <c r="U15" s="41">
+        <v>78.808630393996253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="24" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="38"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="55"/>
-      <c r="T16" s="55"/>
-    </row>
-    <row r="17" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="30" t="s">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="39"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A17" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="27">
         <v>98.8</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="27">
         <v>99.1</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="27">
         <v>98.9</v>
       </c>
-      <c r="G17" s="39">
+      <c r="G17" s="27">
         <v>98.3</v>
       </c>
-      <c r="H17" s="39">
+      <c r="H17" s="27">
         <v>97.2</v>
       </c>
-      <c r="I17" s="39">
+      <c r="I17" s="27">
         <v>97.7</v>
       </c>
-      <c r="J17" s="40">
+      <c r="J17" s="28">
         <v>98.666101597517525</v>
       </c>
-      <c r="K17" s="39">
+      <c r="K17" s="27">
         <v>95.6</v>
       </c>
-      <c r="L17" s="39">
+      <c r="L17" s="27">
         <v>99.1</v>
       </c>
-      <c r="M17" s="40">
+      <c r="M17" s="28">
         <v>97</v>
       </c>
-      <c r="N17" s="39">
+      <c r="N17" s="27">
         <v>94.7</v>
       </c>
-      <c r="O17" s="40">
+      <c r="O17" s="28">
         <v>96.24421478910277</v>
       </c>
-      <c r="P17" s="41">
+      <c r="P17" s="3">
         <v>97.245413942140573</v>
       </c>
-      <c r="Q17" s="56">
+      <c r="Q17" s="36">
         <v>93.789318610145202</v>
       </c>
-      <c r="R17" s="56">
+      <c r="R17" s="36">
         <v>93.37839883628321</v>
       </c>
-      <c r="S17" s="52">
+      <c r="S17" s="36">
         <v>96.389078828315476</v>
       </c>
-      <c r="T17" s="52">
+      <c r="T17" s="36">
         <v>98.924069208908108</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="37" t="s">
+      <c r="U17" s="44">
+        <v>63.072098951393315</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A18" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="29">
         <v>99.2</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="30">
         <v>99</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="31">
         <v>99.9</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="29">
         <v>97.2</v>
       </c>
-      <c r="H18" s="42">
+      <c r="H18" s="29">
         <v>95.7</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="30">
         <v>100</v>
       </c>
-      <c r="J18" s="42">
+      <c r="J18" s="29">
         <v>99.9</v>
       </c>
-      <c r="K18" s="42">
+      <c r="K18" s="29">
         <v>98.9</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="8">
         <v>97.6</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="8">
         <v>99.9</v>
       </c>
-      <c r="N18" s="9">
+      <c r="N18" s="8">
         <v>98.7</v>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="9">
         <v>92.454653583110314</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="9">
         <v>98.254512904669554</v>
       </c>
-      <c r="Q18" s="54">
+      <c r="Q18" s="37">
         <v>98.728938811705589</v>
       </c>
-      <c r="R18" s="54">
+      <c r="R18" s="37">
         <v>93.091416608513612</v>
       </c>
-      <c r="S18" s="53">
+      <c r="S18" s="37">
         <v>95.902649414664197</v>
       </c>
-      <c r="T18" s="53">
+      <c r="T18" s="37">
         <v>96.674394436006068</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A19" s="35" t="s">
+      <c r="U18" s="41">
+        <v>75.090819022457069</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A19" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="29">
         <v>97.8</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="29">
         <v>99.2</v>
       </c>
-      <c r="F19" s="46">
+      <c r="F19" s="31">
         <v>98.3</v>
       </c>
-      <c r="G19" s="45">
+      <c r="G19" s="29">
         <v>98.3</v>
       </c>
-      <c r="H19" s="47">
+      <c r="H19" s="30">
         <v>100</v>
       </c>
-      <c r="I19" s="47">
+      <c r="I19" s="30">
         <v>99</v>
       </c>
-      <c r="J19" s="45">
+      <c r="J19" s="29">
         <v>99.6</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="29">
         <v>91.7</v>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="9">
         <v>100</v>
       </c>
-      <c r="M19" s="11">
+      <c r="M19" s="9">
         <v>95.7</v>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="9">
         <v>88.8</v>
       </c>
-      <c r="O19" s="11">
+      <c r="O19" s="9">
         <v>93.498629613104725</v>
       </c>
-      <c r="P19" s="11">
+      <c r="P19" s="9">
         <v>93.035178795988784</v>
       </c>
-      <c r="Q19" s="53">
+      <c r="Q19" s="37">
         <v>91.334273435401556</v>
       </c>
-      <c r="R19" s="53">
+      <c r="R19" s="37">
         <v>94.815061646117954</v>
       </c>
-      <c r="S19" s="53">
+      <c r="S19" s="37">
         <v>95.851738682785879</v>
       </c>
-      <c r="T19" s="53">
+      <c r="T19" s="37">
         <v>98.675382167807982</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A20" s="35" t="s">
+      <c r="U19" s="41">
+        <v>68.512171236709577</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A20" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="47">
+      <c r="D20" s="30">
         <v>99</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="29">
         <v>99.7</v>
       </c>
-      <c r="F20" s="46">
+      <c r="F20" s="31">
         <v>99.7</v>
       </c>
-      <c r="G20" s="45">
+      <c r="G20" s="29">
         <v>99.2</v>
       </c>
-      <c r="H20" s="45">
+      <c r="H20" s="29">
         <v>96.9</v>
       </c>
-      <c r="I20" s="45">
+      <c r="I20" s="29">
         <v>95.7</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="29">
         <v>97.4</v>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="29">
         <v>95.6</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="8">
         <v>98.9</v>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="8">
         <v>97.7</v>
       </c>
-      <c r="N20" s="12">
+      <c r="N20" s="8">
         <v>95.1</v>
       </c>
-      <c r="O20" s="11">
+      <c r="O20" s="9">
         <v>96.511990034257238</v>
       </c>
-      <c r="P20" s="11">
+      <c r="P20" s="9">
         <v>97.676980074096321</v>
       </c>
-      <c r="Q20" s="53">
+      <c r="Q20" s="37">
         <v>96.098069900886813</v>
       </c>
-      <c r="R20" s="53">
+      <c r="R20" s="37">
         <v>100.53781512605042</v>
       </c>
-      <c r="S20" s="53">
+      <c r="S20" s="37">
         <v>102.7568062228323</v>
       </c>
-      <c r="T20" s="53">
+      <c r="T20" s="37">
         <v>103.36035718481963</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A21" s="35" t="s">
+      <c r="U20" s="41">
+        <v>97.721011770598537</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A21" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="45">
+      <c r="D21" s="29">
         <v>99.4</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="29">
         <v>99.1</v>
       </c>
-      <c r="F21" s="46">
+      <c r="F21" s="31">
         <v>98.9</v>
       </c>
-      <c r="G21" s="45">
+      <c r="G21" s="29">
         <v>99.5</v>
       </c>
-      <c r="H21" s="45">
+      <c r="H21" s="29">
         <v>96.7</v>
       </c>
-      <c r="I21" s="45">
+      <c r="I21" s="29">
         <v>97.6</v>
       </c>
-      <c r="J21" s="45">
+      <c r="J21" s="29">
         <v>97.3</v>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="29">
         <v>97.7</v>
       </c>
-      <c r="L21" s="12">
+      <c r="L21" s="8">
         <v>98.1</v>
       </c>
-      <c r="M21" s="12">
+      <c r="M21" s="8">
         <v>98.1</v>
       </c>
-      <c r="N21" s="11">
+      <c r="N21" s="9">
         <v>97</v>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="9">
         <v>97.646443514644361</v>
       </c>
-      <c r="P21" s="11">
+      <c r="P21" s="9">
         <v>98.140747176368365</v>
       </c>
-      <c r="Q21" s="53">
+      <c r="Q21" s="37">
         <v>96.233183856502251</v>
       </c>
-      <c r="R21" s="53">
+      <c r="R21" s="37">
         <v>100.33525796237662</v>
       </c>
-      <c r="S21" s="53">
+      <c r="S21" s="37">
         <v>99.681465259804895</v>
       </c>
-      <c r="T21" s="53">
+      <c r="T21" s="37">
         <v>98.955001066325437</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A22" s="35" t="s">
+      <c r="U21" s="41">
+        <v>53.779138215210743</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A22" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="45">
+      <c r="D22" s="29">
         <v>98.9</v>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="29">
         <v>99.5</v>
       </c>
-      <c r="F22" s="46">
+      <c r="F22" s="31">
         <v>99.8</v>
       </c>
-      <c r="G22" s="45">
+      <c r="G22" s="29">
         <v>99.7</v>
       </c>
-      <c r="H22" s="45">
+      <c r="H22" s="29">
         <v>94.7</v>
       </c>
-      <c r="I22" s="45">
+      <c r="I22" s="29">
         <v>96.6</v>
       </c>
-      <c r="J22" s="45">
+      <c r="J22" s="29">
         <v>97.9</v>
       </c>
-      <c r="K22" s="45">
+      <c r="K22" s="29">
         <v>96.1</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="9">
         <v>99</v>
       </c>
-      <c r="M22" s="11">
+      <c r="M22" s="9">
         <v>99.2</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="9">
         <v>96.8</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="9">
         <v>98.109160001225831</v>
       </c>
-      <c r="P22" s="11">
+      <c r="P22" s="9">
         <v>99.619945272119182</v>
       </c>
-      <c r="Q22" s="53">
+      <c r="Q22" s="37">
         <v>97.454998783750909</v>
       </c>
-      <c r="R22" s="53">
+      <c r="R22" s="37">
         <v>93.78989283832054</v>
       </c>
-      <c r="S22" s="53">
+      <c r="S22" s="37">
         <v>99.066849759690413</v>
       </c>
-      <c r="T22" s="53">
+      <c r="T22" s="37">
         <v>97.256598055310022</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A23" s="35" t="s">
+      <c r="U22" s="41">
+        <v>66.609692696649219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A23" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="45">
+      <c r="D23" s="29">
         <v>98.6</v>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="29">
         <v>99.2</v>
       </c>
-      <c r="F23" s="46">
+      <c r="F23" s="31">
         <v>97.6</v>
       </c>
-      <c r="G23" s="45">
+      <c r="G23" s="29">
         <v>97.1</v>
       </c>
-      <c r="H23" s="45">
+      <c r="H23" s="29">
         <v>97.7</v>
       </c>
-      <c r="I23" s="45">
+      <c r="I23" s="29">
         <v>98.8</v>
       </c>
-      <c r="J23" s="45">
+      <c r="J23" s="29">
         <v>97.7</v>
       </c>
-      <c r="K23" s="45">
+      <c r="K23" s="29">
         <v>94.3</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="8">
         <v>97.1</v>
       </c>
-      <c r="M23" s="11">
+      <c r="M23" s="9">
         <v>97</v>
       </c>
-      <c r="N23" s="12">
+      <c r="N23" s="8">
         <v>95.6</v>
       </c>
-      <c r="O23" s="11">
+      <c r="O23" s="9">
         <v>98.413291021093897</v>
       </c>
-      <c r="P23" s="11">
+      <c r="P23" s="9">
         <v>95.974889217134418</v>
       </c>
-      <c r="Q23" s="53">
+      <c r="Q23" s="37">
         <v>95.177033492822972</v>
       </c>
-      <c r="R23" s="53">
+      <c r="R23" s="37">
         <v>95.401432340746325</v>
       </c>
-      <c r="S23" s="53">
+      <c r="S23" s="37">
         <v>99.105901053049877</v>
       </c>
-      <c r="T23" s="53">
+      <c r="T23" s="37">
         <v>99.958771387342821</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A24" s="35" t="s">
+      <c r="U23" s="41">
+        <v>73.369320737741788</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A24" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="45">
+      <c r="D24" s="29">
         <v>99.1</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E24" s="29">
         <v>97.4</v>
       </c>
-      <c r="F24" s="46">
+      <c r="F24" s="31">
         <v>98.7</v>
       </c>
-      <c r="G24" s="45">
+      <c r="G24" s="29">
         <v>96.4</v>
       </c>
-      <c r="H24" s="45">
+      <c r="H24" s="29">
         <v>97.1</v>
       </c>
-      <c r="I24" s="45">
+      <c r="I24" s="29">
         <v>96.4</v>
       </c>
-      <c r="J24" s="45">
+      <c r="J24" s="29">
         <v>99.3</v>
       </c>
-      <c r="K24" s="45">
+      <c r="K24" s="29">
         <v>96.5</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="8">
         <v>98.6</v>
       </c>
-      <c r="M24" s="11">
+      <c r="M24" s="9">
         <v>95</v>
       </c>
-      <c r="N24" s="12">
+      <c r="N24" s="8">
         <v>96.3</v>
       </c>
-      <c r="O24" s="11">
+      <c r="O24" s="9">
         <v>97.438130155820346</v>
       </c>
-      <c r="P24" s="11">
+      <c r="P24" s="9">
         <v>99.45064923272497</v>
       </c>
-      <c r="Q24" s="53">
+      <c r="Q24" s="37">
         <v>97.514721565354478</v>
       </c>
-      <c r="R24" s="53">
+      <c r="R24" s="37">
         <v>92.308748798242007</v>
       </c>
-      <c r="S24" s="53">
+      <c r="S24" s="37">
         <v>100.16892783614</v>
       </c>
-      <c r="T24" s="53">
+      <c r="T24" s="37">
         <v>101.43668918194489</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A25" s="35" t="s">
+      <c r="U24" s="41">
+        <v>62.858047159360666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A25" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="35" t="s">
+      <c r="B25" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="45">
+      <c r="D25" s="29">
         <v>99.8</v>
       </c>
-      <c r="E25" s="45">
+      <c r="E25" s="29">
         <v>99.9</v>
       </c>
-      <c r="F25" s="46">
+      <c r="F25" s="31">
         <v>98.6</v>
       </c>
-      <c r="G25" s="47">
+      <c r="G25" s="30">
         <v>99</v>
       </c>
-      <c r="H25" s="45">
+      <c r="H25" s="29">
         <v>97.4</v>
       </c>
-      <c r="I25" s="45">
+      <c r="I25" s="29">
         <v>97.7</v>
       </c>
-      <c r="J25" s="45">
+      <c r="J25" s="29">
         <v>98.4</v>
       </c>
-      <c r="K25" s="45">
+      <c r="K25" s="29">
         <v>95.6</v>
       </c>
-      <c r="L25" s="15">
+      <c r="L25" s="9">
         <v>99.8</v>
       </c>
-      <c r="M25" s="15">
+      <c r="M25" s="9">
         <v>95.1</v>
       </c>
-      <c r="N25" s="15">
+      <c r="N25" s="9">
         <v>91.7</v>
       </c>
-      <c r="O25" s="15">
+      <c r="O25" s="9">
         <v>96.281061826817066</v>
       </c>
-      <c r="P25" s="15">
+      <c r="P25" s="9">
         <v>96.444387118964698</v>
       </c>
-      <c r="Q25" s="53">
+      <c r="Q25" s="37">
         <v>83.697507681802662</v>
       </c>
-      <c r="R25" s="53">
+      <c r="R25" s="37">
         <v>89.338842975206617</v>
       </c>
-      <c r="S25" s="53">
+      <c r="S25" s="37">
         <v>87.061971344726402</v>
       </c>
-      <c r="T25" s="53">
+      <c r="T25" s="37">
         <v>99.985767825798192</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A26" s="35" t="s">
+      <c r="U25" s="41">
+        <v>42.889466589639902</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A26" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="45">
+      <c r="D26" s="29">
         <v>98.8</v>
       </c>
-      <c r="E26" s="45">
+      <c r="E26" s="29">
         <v>98.9</v>
       </c>
-      <c r="F26" s="46">
+      <c r="F26" s="31">
         <v>98.2</v>
       </c>
-      <c r="G26" s="45">
+      <c r="G26" s="29">
         <v>97.4</v>
       </c>
-      <c r="H26" s="45">
+      <c r="H26" s="29">
         <v>99.7</v>
       </c>
-      <c r="I26" s="45">
+      <c r="I26" s="29">
         <v>98.1</v>
       </c>
-      <c r="J26" s="45">
+      <c r="J26" s="29">
         <v>98.7</v>
       </c>
-      <c r="K26" s="45">
+      <c r="K26" s="29">
         <v>99.9</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="8">
         <v>99.7</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="8">
         <v>96.8</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="8">
         <v>97.7</v>
       </c>
-      <c r="O26" s="15">
+      <c r="O26" s="9">
         <v>99.425085063944621</v>
       </c>
-      <c r="P26" s="15">
+      <c r="P26" s="9">
         <v>97.981882811604166</v>
       </c>
-      <c r="Q26" s="53">
+      <c r="Q26" s="37">
         <v>93.662126537785582</v>
       </c>
-      <c r="R26" s="53">
+      <c r="R26" s="37">
         <v>87.955555555555549</v>
       </c>
-      <c r="S26" s="54">
+      <c r="S26" s="37">
         <v>95.855752718946761</v>
       </c>
-      <c r="T26" s="54">
+      <c r="T26" s="37">
         <v>96.197502837684439</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" ht="36" x14ac:dyDescent="0.2">
-      <c r="A27" s="24" t="s">
+      <c r="U26" s="41">
+        <v>51.876172607879923</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="36" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="2"/>
@@ -2857,24 +2868,21 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="51"/>
-      <c r="S27" s="51"/>
-      <c r="T27" s="51"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A28" s="31" t="s">
+      <c r="P27" s="7"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="35"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="39"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A28" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="24" t="s">
         <v>18</v>
       </c>
       <c r="D28" s="4" t="s">
@@ -2901,42 +2909,45 @@
       <c r="K28" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L28" s="18">
+      <c r="L28" s="11">
         <v>96.8</v>
       </c>
-      <c r="M28" s="18">
+      <c r="M28" s="11">
         <v>97.2</v>
       </c>
-      <c r="N28" s="18">
+      <c r="N28" s="11">
         <v>94.2</v>
       </c>
-      <c r="O28" s="18">
+      <c r="O28" s="11">
         <v>92</v>
       </c>
-      <c r="P28" s="22">
+      <c r="P28" s="3">
         <v>95.083643367898887</v>
       </c>
-      <c r="Q28" s="52">
+      <c r="Q28" s="36">
         <v>88.782541857434083</v>
       </c>
-      <c r="R28" s="52">
+      <c r="R28" s="36">
         <v>89.631204460036727</v>
       </c>
-      <c r="S28" s="52">
+      <c r="S28" s="36">
         <v>92.843773094907561</v>
       </c>
-      <c r="T28" s="52">
+      <c r="T28" s="36">
         <v>70.95917476179909</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A29" s="35" t="s">
+      <c r="U28" s="44">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A29" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="26" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="4" t="s">
@@ -2963,42 +2974,45 @@
       <c r="K29" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="12">
         <v>97.3</v>
       </c>
-      <c r="M29" s="19">
+      <c r="M29" s="12">
         <v>99.3</v>
       </c>
-      <c r="N29" s="19">
+      <c r="N29" s="12">
         <v>96.3</v>
       </c>
-      <c r="O29" s="19">
+      <c r="O29" s="12">
         <v>94.6</v>
       </c>
-      <c r="P29" s="15">
+      <c r="P29" s="9">
         <v>99.597511891694111</v>
       </c>
-      <c r="Q29" s="53">
+      <c r="Q29" s="37">
         <v>83.44010727056019</v>
       </c>
-      <c r="R29" s="53">
+      <c r="R29" s="37">
         <v>89.204466154919743</v>
       </c>
-      <c r="S29" s="53">
+      <c r="S29" s="37">
         <v>95.656192236598898</v>
       </c>
-      <c r="T29" s="53">
+      <c r="T29" s="37">
         <v>71.980174274522341</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A30" s="35" t="s">
+      <c r="U29" s="41">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A30" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="35" t="s">
+      <c r="B30" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="26" t="s">
         <v>20</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -3025,42 +3039,45 @@
       <c r="K30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="12">
         <v>97.3</v>
       </c>
-      <c r="M30" s="19">
+      <c r="M30" s="12">
         <v>95.9</v>
       </c>
-      <c r="N30" s="19">
+      <c r="N30" s="12">
         <v>94.5</v>
       </c>
-      <c r="O30" s="19">
+      <c r="O30" s="12">
         <v>93.8</v>
       </c>
-      <c r="P30" s="15">
+      <c r="P30" s="9">
         <v>90.08985713362209</v>
       </c>
-      <c r="Q30" s="53">
+      <c r="Q30" s="37">
         <v>88.195819212830926</v>
       </c>
-      <c r="R30" s="53">
+      <c r="R30" s="37">
         <v>84.751749416861045</v>
       </c>
-      <c r="S30" s="53">
+      <c r="S30" s="37">
         <v>91.580590521106643</v>
       </c>
-      <c r="T30" s="53">
+      <c r="T30" s="37">
         <v>58.933388669848519</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A31" s="35" t="s">
+      <c r="U30" s="41">
+        <v>85.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A31" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="26" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="4" t="s">
@@ -3087,42 +3104,45 @@
       <c r="K31" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="12">
         <v>98.2</v>
       </c>
-      <c r="M31" s="19">
+      <c r="M31" s="12">
         <v>96.4</v>
       </c>
-      <c r="N31" s="19">
+      <c r="N31" s="12">
         <v>96.3</v>
       </c>
-      <c r="O31" s="19">
+      <c r="O31" s="12">
         <v>95</v>
       </c>
-      <c r="P31" s="15">
+      <c r="P31" s="9">
         <v>94.992817566181003</v>
       </c>
-      <c r="Q31" s="53">
+      <c r="Q31" s="37">
         <v>88.268864933417873</v>
       </c>
-      <c r="R31" s="53">
+      <c r="R31" s="37">
         <v>96.201680672268907</v>
       </c>
-      <c r="S31" s="53">
+      <c r="S31" s="37">
         <v>97.643559826126747</v>
       </c>
-      <c r="T31" s="53">
+      <c r="T31" s="37">
         <v>90.894136999177533</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A32" s="35" t="s">
+      <c r="U31" s="41">
+        <v>95.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A32" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="26" t="s">
         <v>22</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -3149,42 +3169,45 @@
       <c r="K32" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L32" s="19">
+      <c r="L32" s="12">
         <v>96.8</v>
       </c>
-      <c r="M32" s="19">
+      <c r="M32" s="12">
         <v>96.7</v>
       </c>
-      <c r="N32" s="19">
+      <c r="N32" s="12">
         <v>97</v>
       </c>
-      <c r="O32" s="19">
+      <c r="O32" s="12">
         <v>95.1</v>
       </c>
-      <c r="P32" s="15">
+      <c r="P32" s="9">
         <v>97.283380681818173</v>
       </c>
-      <c r="Q32" s="53">
+      <c r="Q32" s="37">
         <v>91.250903832248724</v>
       </c>
-      <c r="R32" s="53">
+      <c r="R32" s="37">
         <v>95.567144719687093</v>
       </c>
-      <c r="S32" s="53">
+      <c r="S32" s="37">
         <v>95.022894684451515</v>
       </c>
-      <c r="T32" s="53">
+      <c r="T32" s="37">
         <v>83.066751972702065</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A33" s="35" t="s">
+      <c r="U32" s="41">
+        <v>89.9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A33" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="35" t="s">
+      <c r="B33" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="26" t="s">
         <v>23</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -3211,42 +3234,45 @@
       <c r="K33" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="12">
         <v>96.3</v>
       </c>
-      <c r="M33" s="19">
+      <c r="M33" s="12">
         <v>98.8</v>
       </c>
-      <c r="N33" s="19">
+      <c r="N33" s="12">
         <v>97.2</v>
       </c>
-      <c r="O33" s="19">
+      <c r="O33" s="12">
         <v>92.1</v>
       </c>
-      <c r="P33" s="15">
+      <c r="P33" s="9">
         <v>98.414509639060725</v>
       </c>
-      <c r="Q33" s="53">
+      <c r="Q33" s="37">
         <v>95.711274704462852</v>
       </c>
-      <c r="R33" s="53">
+      <c r="R33" s="37">
         <v>91.330444457457389</v>
       </c>
-      <c r="S33" s="53">
+      <c r="S33" s="37">
         <v>96.0270894451033</v>
       </c>
-      <c r="T33" s="53">
+      <c r="T33" s="37">
         <v>63.344487940396512</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A34" s="35" t="s">
+      <c r="U33" s="41">
+        <v>97.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A34" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="35" t="s">
+      <c r="B34" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="26" t="s">
         <v>24</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -3273,42 +3299,45 @@
       <c r="K34" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L34" s="19">
+      <c r="L34" s="12">
         <v>97.2</v>
       </c>
-      <c r="M34" s="19">
+      <c r="M34" s="12">
         <v>96.1</v>
       </c>
-      <c r="N34" s="19">
+      <c r="N34" s="12">
         <v>94</v>
       </c>
-      <c r="O34" s="19">
+      <c r="O34" s="12">
         <v>96</v>
       </c>
-      <c r="P34" s="15">
+      <c r="P34" s="9">
         <v>94.2978409300609</v>
       </c>
-      <c r="Q34" s="53">
+      <c r="Q34" s="37">
         <v>95.762224352828383</v>
       </c>
-      <c r="R34" s="53">
+      <c r="R34" s="37">
         <v>91.368262344515642</v>
       </c>
-      <c r="S34" s="53">
+      <c r="S34" s="37">
         <v>90.224518180011927</v>
       </c>
-      <c r="T34" s="53">
+      <c r="T34" s="37">
         <v>78.045763760049468</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A35" s="35" t="s">
+      <c r="U34" s="41">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A35" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="35" t="s">
+      <c r="B35" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="26" t="s">
         <v>25</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -3335,42 +3364,45 @@
       <c r="K35" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L35" s="19">
+      <c r="L35" s="12">
         <v>97.6</v>
       </c>
-      <c r="M35" s="19">
+      <c r="M35" s="12">
         <v>98.7</v>
       </c>
-      <c r="N35" s="19">
+      <c r="N35" s="12">
         <v>92.6</v>
       </c>
-      <c r="O35" s="19">
+      <c r="O35" s="12">
         <v>92.1</v>
       </c>
-      <c r="P35" s="15">
+      <c r="P35" s="9">
         <v>94.916127823071875</v>
       </c>
-      <c r="Q35" s="53">
+      <c r="Q35" s="37">
         <v>90.95590300533658</v>
       </c>
-      <c r="R35" s="53">
+      <c r="R35" s="37">
         <v>92.345373803964662</v>
       </c>
-      <c r="S35" s="53">
+      <c r="S35" s="37">
         <v>94.65237818719315</v>
       </c>
-      <c r="T35" s="53">
+      <c r="T35" s="37">
         <v>85.150637932883029</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A36" s="35" t="s">
+      <c r="U35" s="41">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A36" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="35" t="s">
+      <c r="B36" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="26" t="s">
         <v>26</v>
       </c>
       <c r="D36" s="4" t="s">
@@ -3397,97 +3429,103 @@
       <c r="K36" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="12">
         <v>95</v>
       </c>
-      <c r="M36" s="19">
+      <c r="M36" s="12">
         <v>94.8</v>
       </c>
-      <c r="N36" s="19">
+      <c r="N36" s="12">
         <v>90.4</v>
       </c>
-      <c r="O36" s="19">
+      <c r="O36" s="12">
         <v>83.4</v>
       </c>
-      <c r="P36" s="15">
+      <c r="P36" s="9">
         <v>93.823490842330727</v>
       </c>
-      <c r="Q36" s="53">
+      <c r="Q36" s="37">
         <v>79.37812567949554</v>
       </c>
-      <c r="R36" s="53">
+      <c r="R36" s="37">
         <v>88.660287081339717</v>
       </c>
-      <c r="S36" s="53">
+      <c r="S36" s="37">
         <v>86.721042637666145</v>
       </c>
-      <c r="T36" s="53">
+      <c r="T36" s="37">
         <v>74.771099198254191</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="48" t="s">
+      <c r="U36" s="41">
+        <v>70.099999999999994</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="48" t="s">
+      <c r="B37" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="C37" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="D37" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I37" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="J37" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="L37" s="26">
+      <c r="D37" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37" s="18">
         <v>97.9</v>
       </c>
-      <c r="M37" s="26">
+      <c r="M37" s="18">
         <v>96.8</v>
       </c>
-      <c r="N37" s="26">
+      <c r="N37" s="18">
         <v>90</v>
       </c>
-      <c r="O37" s="26">
+      <c r="O37" s="18">
         <v>93.9</v>
       </c>
-      <c r="P37" s="50">
+      <c r="P37" s="34">
         <v>95.896253602305464</v>
       </c>
-      <c r="Q37" s="58">
+      <c r="Q37" s="38">
         <v>87.352779306549252</v>
       </c>
-      <c r="R37" s="58">
+      <c r="R37" s="38">
         <v>84.944444444444443</v>
       </c>
-      <c r="S37" s="58">
+      <c r="S37" s="38">
         <v>89.112764739553512</v>
       </c>
-      <c r="T37" s="58">
+      <c r="T37" s="38">
         <v>67.582292849035184</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U37" s="38">
+        <v>81.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -3497,36 +3535,10 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="57"/>
-      <c r="R38" s="57"/>
-      <c r="S38" s="57"/>
-      <c r="T38" s="16"/>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16"/>
-      <c r="P41" s="16"/>
+      <c r="Q38" s="35"/>
+      <c r="R38" s="35"/>
+      <c r="S38" s="35"/>
+      <c r="U38" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
